--- a/coach_data.xlsx
+++ b/coach_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W13"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,114 +441,104 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Commission Status</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Railway</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Coach Type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Base Depot</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Owning Division</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Manufacture</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Workshop</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Built Date</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Factory Turn Out Date</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Fitness Type</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Commission Date</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Gauge</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Coupling Type</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Tare Weight</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Commission Date(DD/MM/YYYY</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Base Depot</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Coach Category</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Fitness Type</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Max Speed</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Factory TurnOut Date</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Maintenance Zone</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Last POH/SS2/SS3 Workshop</t>
-        </is>
-      </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>POH/SS2/SS3 Date</t>
+          <t>Power Generation Type</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>IOH/SS1 Date</t>
+          <t>Tare Weight(In Tonnes)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Expected IOH/SS1 Due Date</t>
+          <t>Is Parcel Coach</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Maintenance Depot</t>
+          <t>Is Parcel Facility Available</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Manufactured By</t>
+          <t>Parcel Capacity Weight</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Return Date</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>IOH/SS1 Location</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Extended Return Date</t>
+          <t>Parcel Capacity Volume</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WR-201504</t>
+          <t>201504</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -558,105 +548,95 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>COMMISSIONED</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>LWACCN</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>BDTS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>BCT</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>LPLW</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>14/07/2020</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>14/07/2020</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>MAIL EXP SUF</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>03/09/2020</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>BG</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>CBC</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>LHB</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>EOG</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>47.47</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>03/09/2020</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>BDTS</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>LHB</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>MLEXSF</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>14/07/2020</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>LPLW</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>05/08/2023</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>31/01/2025</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>BVC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -665,7 +645,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WR-193915</t>
+          <t>193915</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -675,105 +655,95 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>COMMISSIONED</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>LWSCN</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>KKF</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ADI</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>LPLW</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>14/06/2019</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>14/06/2019</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>MAIL EXP SUF</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>14/06/2019</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>BG</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CBC</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>LHB</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>EOG</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>44.23</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>14/06/2019</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>KKF</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>LHB</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>MLEXSF</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>14/06/2019</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>BPLW</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>30/08/2022</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>MMCT</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
-        <is>
-          <t>31/10/2025</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>MMCT</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -782,7 +752,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WR-031080</t>
+          <t>259076</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -792,52 +762,52 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LWACCN</t>
+          <t>TURNOUT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>31/07/2003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>17/12/2003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MMCT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>LHB</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>RAJDHN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -847,17 +817,17 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>LPLW</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -867,30 +837,20 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>09/09/2027</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>BVC</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>RCF</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
-        <is>
-          <t>30/04/2029</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>DADN</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -899,7 +859,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WR-041010</t>
+          <t>169272</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -909,105 +869,95 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LWACCN</t>
+          <t>COMMISSIONED</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>09/07/2004</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>WGSCN</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VRL</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>BVC</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ICF</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>BVCW</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>24/05/2016</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>11/12/2019</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Select...</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>20/04/2022</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>BG</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>CBC</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>47.47</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>09/07/2004</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>MMCT</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>LHB</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>RAJDHN</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>AICW</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>17/10/2022</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>KKF</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>RCF</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
-        <is>
-          <t>30/11/2025</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>KKF</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1016,7 +966,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WR-196188</t>
+          <t>974388</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1026,105 +976,95 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LWACCN</t>
+          <t>COMMISSIONED</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13/11/2019</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>RCC</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>BVC</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>BVC</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Select...</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Select...</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Select...</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>BG</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>CBC</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>47.47</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>18/03/2020</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>BDTS</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>LHB</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>MLEXSF</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>13/11/2019</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>LPLW</t>
+          <t>OCVS</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>19/08/2027</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>KKF</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>RCF</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
-        <is>
-          <t>31/03/2029</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>SBI</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1133,7 +1073,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WR-169272</t>
+          <t>028760</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1143,105 +1083,95 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>WGSCN</t>
+          <t>COMMISSIONED</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>24/05/2016</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>RAAC</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>MMCT</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>BCT</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ICF</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>LPLW</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>15/04/2002</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>15/04/2002</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>MAIL EXP SUF</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>15/04/2002</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>BG</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SCREW</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>41.85</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>20/04/2022</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>VRL</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>ICF</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>MLEXS</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>11/12/2019</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>LPLW</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>28/11/2026</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
-        <is>
-          <t>31/10/2027</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>BL</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1250,7 +1180,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WR-974388</t>
+          <t>194798</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1260,87 +1190,87 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RCC</t>
+          <t>COMMISSIONED</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>LWACCN</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>MMCT</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>BCT</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>LPLW</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>14/10/2019</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>14/10/2019</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>MAIL EXP SUF</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>18/03/2020</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>BG</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>CBC</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>40.25</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>BVC</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>OCVS</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>MLEXS</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LHB</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>20/11/2019</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1349,16 +1279,6 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
-        <is>
-          <t>20/12/2023</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1367,7 +1287,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WR-028760</t>
+          <t>041244</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1377,114 +1297,104 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RAAC</t>
+          <t>COMMISSIONED</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>15/04/2002</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>LWACCW</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>MMCT</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>BCT</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>RCF</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>LPLW</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>31/03/2004</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>MAIL EXP SUF</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>31/03/2004</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>BG</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>CBC</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>47.0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>15/04/2002</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>MMCT</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ICF</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>MLEXSF</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>15/04/2002</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>LPLW</t>
+          <t>LHB</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>13/10/2021</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>MMCT</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>28/10/2025</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>MMCT</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>31/01/2026</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WR-194798</t>
+          <t>196182</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1494,105 +1404,95 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>COMMISSIONED</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>LWACCN</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>14/10/2019</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ADI</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ADI</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>LPLW</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>07/11/2019</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>07/11/2019</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>MAIL EXP SUF</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>15/11/2019</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>BG</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>CBC</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>LHB</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>EOG</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>47.47</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>18/03/2020</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>MMCT</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>LHB</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>MLEXSF</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>14/10/2019</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>LPLW</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>29/11/2022</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>BDTS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
-        <is>
-          <t>31/01/2026</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>BDTS</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1601,7 +1501,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WR-041244</t>
+          <t>193891</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1611,339 +1511,95 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LWACCW</t>
+          <t>COMMISSIONED</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>31/03/2004</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>LWACCN</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>MMCT</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>BCT</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>LPLW</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>17/07/2019</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>17/07/2019</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>RAJDHANI</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>20/07/2019</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>BG</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>CBC</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>31/03/2004</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>MMCT</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>LHB</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>MLEXSF</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>LPLW</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>29/07/2021</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>BL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>RCF</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
-        <is>
-          <t>30/09/2024</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>LPLW</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>WR-196182</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LWACCN</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>07/11/2019</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>BG</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>CBC</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>47.47</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>15/11/2019</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>ADI</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>LHB</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>MLEXSF</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>07/11/2019</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>LPLW</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>27/02/2026</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>29/08/2027</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>BVC</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>RCF</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>30/04/2029</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>KKF</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>WR-193891</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LWACCN</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>17/07/2019</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>BG</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>CBC</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>47.47</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>20/07/2019</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>MMCT</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>LHB</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>RAJDHN</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>17/07/2019</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>AICW</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>11/12/2022</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>KKF</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>ICF</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>31/01/2026</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>BHUJ</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
